--- a/Examples/Powder_Raman/Vasp/results.ref.xlsx
+++ b/Examples/Powder_Raman/Vasp/results.ref.xlsx
@@ -130,13 +130,13 @@
     <t>Absorption maximum (L/mole/cm)</t>
   </si>
   <si>
-    <t>Raman R_total (Å4/amu)</t>
+    <t>Raman R_total (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_parallel (Å4/amu)</t>
+    <t>Raman R_parallel (Å⁴/amu)</t>
   </si>
   <si>
-    <t>Raman R_perp (Å4/amu)</t>
+    <t>Raman R_perp (Å⁴/amu)</t>
   </si>
   <si>
     <t>No</t>
@@ -1142,13 +1142,13 @@
         <v>4.241949360419647E-17</v>
       </c>
       <c r="I26">
-        <v>0.0003694925816768152</v>
+        <v>0.0001136766582418394</v>
       </c>
       <c r="J26">
-        <v>0.0002186080135572942</v>
+        <v>6.725609573351615E-05</v>
       </c>
       <c r="K26">
-        <v>0.000150884568119521</v>
+        <v>4.642056250832323E-05</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1174,13 +1174,13 @@
         <v>6.348338572202158E-15</v>
       </c>
       <c r="I27">
-        <v>0.0009396336392249688</v>
+        <v>0.0002890840503318687</v>
       </c>
       <c r="J27">
-        <v>0.0006764144495892957</v>
+        <v>0.0002081030527510292</v>
       </c>
       <c r="K27">
-        <v>0.0002632191896356731</v>
+        <v>8.098099758083952E-05</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1206,13 +1206,13 @@
         <v>1.235580493864296E-15</v>
       </c>
       <c r="I28">
-        <v>0.00351909773693836</v>
+        <v>0.001082671995594963</v>
       </c>
       <c r="J28">
-        <v>0.002788846748203684</v>
+        <v>0.0008580058014851017</v>
       </c>
       <c r="K28">
-        <v>0.0007302509887346757</v>
+        <v>0.000224666194109861</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1238,13 +1238,13 @@
         <v>1.45794737166681E-06</v>
       </c>
       <c r="I29">
-        <v>1.130139704001208</v>
+        <v>0.3476944092199619</v>
       </c>
       <c r="J29">
-        <v>0.6750682637717818</v>
+        <v>0.2076888904303323</v>
       </c>
       <c r="K29">
-        <v>0.4550714402294256</v>
+        <v>0.1400055187896294</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1270,13 +1270,13 @@
         <v>3.79777019590013E-09</v>
       </c>
       <c r="I30">
-        <v>1.906354221847179</v>
+        <v>0.5865015648794752</v>
       </c>
       <c r="J30">
-        <v>1.066211397870491</v>
+        <v>0.3280264738719186</v>
       </c>
       <c r="K30">
-        <v>0.8401428239766887</v>
+        <v>0.2584750910075566</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1302,13 +1302,13 @@
         <v>6.885355802195763E-09</v>
       </c>
       <c r="I31">
-        <v>0.0001224081298753455</v>
+        <v>3.76596116834447E-05</v>
       </c>
       <c r="J31">
-        <v>8.764306433652186E-05</v>
+        <v>2.696392611358207E-05</v>
       </c>
       <c r="K31">
-        <v>3.476506553882365E-05</v>
+        <v>1.069568556986263E-05</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1334,13 +1334,13 @@
         <v>9152.411971399288</v>
       </c>
       <c r="I32">
-        <v>244.5650949644847</v>
+        <v>75.2419509804334</v>
       </c>
       <c r="J32">
-        <v>194.1474204885265</v>
+        <v>59.73064429941098</v>
       </c>
       <c r="K32">
-        <v>50.41767447595816</v>
+        <v>15.51130668102241</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -1366,13 +1366,13 @@
         <v>8782.737712114529</v>
       </c>
       <c r="I33">
-        <v>12.53336035515977</v>
+        <v>3.855965159705168</v>
       </c>
       <c r="J33">
-        <v>7.178912951480183</v>
+        <v>2.208636585962976</v>
       </c>
       <c r="K33">
-        <v>5.354447403679585</v>
+        <v>1.647328573742192</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -1398,13 +1398,13 @@
         <v>8782.881321962346</v>
       </c>
       <c r="I34">
-        <v>12.49092521912163</v>
+        <v>3.84290972991829</v>
       </c>
       <c r="J34">
-        <v>7.138256696552334</v>
+        <v>2.196128439856625</v>
       </c>
       <c r="K34">
-        <v>5.352668522569295</v>
+        <v>1.646781290061665</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -1430,13 +1430,13 @@
         <v>1.650883674762879E-08</v>
       </c>
       <c r="I35">
-        <v>3.30954491205609</v>
+        <v>1.018201784177864</v>
       </c>
       <c r="J35">
-        <v>1.892226800840505</v>
+        <v>0.5821551771865852</v>
       </c>
       <c r="K35">
-        <v>1.417318111215585</v>
+        <v>0.4360466069912792</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -1462,13 +1462,13 @@
         <v>7.640155293983162E-07</v>
       </c>
       <c r="I36">
-        <v>3.198407531985151</v>
+        <v>0.9840096877766762</v>
       </c>
       <c r="J36">
-        <v>1.836160019141218</v>
+        <v>0.5649058880316425</v>
       </c>
       <c r="K36">
-        <v>1.362247512843933</v>
+        <v>0.4191037997450336</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -1494,13 +1494,13 @@
         <v>1.588164640940567E-07</v>
       </c>
       <c r="I37">
-        <v>0.0003103615006490657</v>
+        <v>9.548461861019829E-05</v>
       </c>
       <c r="J37">
-        <v>0.0002725673458659361</v>
+        <v>8.385701516191348E-05</v>
       </c>
       <c r="K37">
-        <v>3.779415478312953E-05</v>
+        <v>1.162760344828481E-05</v>
       </c>
     </row>
   </sheetData>
